--- a/samples/通信データExcel_サンプル.xlsx
+++ b/samples/通信データExcel_サンプル.xlsx
@@ -500,7 +500,7 @@
         <v/>
       </c>
       <c r="AH1" t="str">
-        <v>Engine_10_00_CONN_E2</v>
+        <v>Engine_10_CONN_E2</v>
       </c>
       <c r="AI1" t="str">
         <v/>
